--- a/python/configs/业绩技术指标模板.xlsx
+++ b/python/configs/业绩技术指标模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>查询ID(软件使用)</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>项目所起作用</t>
+  </si>
+  <si>
+    <t>企业名称</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1011,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.625" style="2" customWidth="1"/>
@@ -1021,10 +1024,11 @@
     <col min="8" max="8" width="15.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="23.5" style="3" customWidth="1"/>
     <col min="10" max="10" width="18.375" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="45" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,6 +1059,9 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
